--- a/assets/constructions/examples/ctd_mie_single.xlsx
+++ b/assets/constructions/examples/ctd_mie_single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,53 +569,75 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BF-C12-4R-130-1T</t>
+          <t>R216F-20A20S-075</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>CoroMillⓇ 216F ball nose milling cutter</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>130</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>25</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="H2" t="n">
+        <v>141</v>
+      </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>40000</v>
+      </c>
       <c r="M2" t="n">
-        <v>0.1</v>
+        <v>0.44</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>P3200-D08</t>
+          <t>CoroMill 216F (R216F-2050)</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -636,61 +658,63 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>DER_P3200-D08</t>
+          <t>COR_R216F:20H</t>
         </is>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>P32*D08</t>
+          <t>SAND_R216F-2050_H</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R216F-25A25S-045</t>
+          <t>010E62090-02-U010150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CoroMillⓇ 216F ball nose milling cutter</t>
-        </is>
-      </c>
+          <t>PALBIT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>150</v>
+      </c>
       <c r="G3" t="n">
-        <v>25</v>
-      </c>
-      <c r="H3" t="n">
-        <v>121</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>2</v>
       </c>
@@ -698,20 +722,14 @@
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>40000</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>0.54</v>
+        <v>0.15</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>CoroMill 216F (R216F-2560)</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
@@ -723,19 +741,21 @@
           <t>HA</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
         <v>1</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>COR_R216F:25H</t>
+          <t>PALB_WC10H</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -744,164 +764,174 @@
       <c r="Y3" t="n">
         <v>2</v>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>SAND_R216F-2560_H</t>
-        </is>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
-      </c>
+          <t>2022/PALBIT Главный каталог</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M270TD010A10L120C</t>
+          <t>BF-C20-10R-160-1T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M270</t>
+          <t>BF</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>57000</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M270TF10R..</t>
+          <t>P3200-D20</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>HA</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
         <v>1</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>WIDIA_M2F10H</t>
+          <t>DER_P3200-D20</t>
         </is>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>WID_M2F10_H</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>WID_M270TD_1197</t>
-        </is>
-      </c>
+          <t>P32*D20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2017 / WIDIA основной каталог EN</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>4378.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BF-C16-8R-200-1T</t>
+          <t>M270BD012B12L95</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>M270</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>55000</v>
+      </c>
       <c r="M5" t="n">
-        <v>0.29</v>
+        <v>0.1</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>P3200-D16</t>
+          <t>M270B.12</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -912,7 +942,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -922,36 +952,46 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>HA-16</t>
+          <t>HB-12</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>DER_P3200-D16</t>
+          <t>WIDIA_M2B12H</t>
         </is>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>P32*D16</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+          <t>WID_M2B12_H</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>WID_M270BD_1143</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA основной каталог EN</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BF-C25-12.5R-250-1T</t>
+          <t>BF-C32-12.5R-200-1T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -968,13 +1008,13 @@
         <v>25</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
@@ -986,7 +1026,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="N6" t="n">
         <v>12.5</v>
@@ -1014,7 +1054,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HA-32</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1039,6 +1079,12 @@
           <t>2019 / DEREK</t>
         </is>
       </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
